--- a/artfynd/A 975-2023 artfynd.xlsx
+++ b/artfynd/A 975-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 975-2023 artfynd.xlsx
+++ b/artfynd/A 975-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>107306247</v>
       </c>
       <c r="B2" t="n">
-        <v>9491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -721,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589710.4883737793</v>
+        <v>589710</v>
       </c>
       <c r="R2" t="n">
-        <v>6412934.593786189</v>
+        <v>6412935</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,19 +749,9 @@
           <t>2023-03-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-03-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
